--- a/dama/cases/营收系统数据标准/2 服务类/2.2 客户管理数据/2.2.1 客户基础信息/2. 联系人信息.xlsx
+++ b/dama/cases/营收系统数据标准/2 服务类/2.2 客户管理数据/2.2.1 客户基础信息/2. 联系人信息.xlsx
@@ -581,7 +581,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -612,13 +612,6 @@
       <sz val="10"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1119,48 +1112,51 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -1170,97 +1166,94 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2906,7 +2899,7 @@
         <v>96</v>
       </c>
       <c r="R14" s="15">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="S14" s="15" t="s">
         <v>75</v>
@@ -2998,7 +2991,7 @@
         <v>96</v>
       </c>
       <c r="R15" s="15">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="S15" s="15" t="s">
         <v>75</v>
